--- a/data/data_monitoreo_san_antonio_bajo.xlsx
+++ b/data/data_monitoreo_san_antonio_bajo.xlsx
@@ -447,127 +447,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIRADO PEREZ JEINER</t>
+          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MEDINA VALLEJOS ERICK LEONARDO</t>
+          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>SOTO VILLENA NILSON</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
+          <t>PÓSITO CHUGDEN NANIX</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>106</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOTO VALLEJOS ELSITA</t>
+          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOTO VILLENA NILSON</t>
+          <t>SOTO VALLEJOS ELSITA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BENAVIDES MARRUFO ARACELI</t>
+          <t>VASQUEZ LUNA YUDITH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PÓSITO CHUGDEN NANIX</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>BENAVIDES MARRUFO ARACELI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
+          <t>BENAVIDES SALAZAR IDELSA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VASQUEZ LUNA YUDITH</t>
+          <t>TIRADO PEREZ JEINER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BENAVIDES SALAZAR IDELSA</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_san_antonio_bajo.xlsx
+++ b/data/data_monitoreo_san_antonio_bajo.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
@@ -457,57 +457,57 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
+          <t>SOTO VILLENA NILSON</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOTO VILLENA NILSON</t>
+          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PÓSITO CHUGDEN NANIX</t>
+          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
+          <t>SOTO VALLEJOS ELSITA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOTO VALLEJOS ELSITA</t>
+          <t>PÓSITO CHUGDEN NANIX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
@@ -517,47 +517,47 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>TIRADO PEREZ JEINER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BENAVIDES MARRUFO ARACELI</t>
+          <t>BENAVIDES SALAZAR IDELSA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BENAVIDES SALAZAR IDELSA</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TIRADO PEREZ JEINER</t>
+          <t>BENAVIDES MARRUFO ARACELI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_san_antonio_bajo.xlsx
+++ b/data/data_monitoreo_san_antonio_bajo.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9">
@@ -523,21 +523,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TIRADO PEREZ JEINER</t>
+          <t>BENAVIDES SALAZAR IDELSA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BENAVIDES SALAZAR IDELSA</t>
+          <t>TIRADO PEREZ JEINER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
@@ -547,27 +547,27 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BENAVIDES MARRUFO ARACELI</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>BENAVIDES MARRUFO ARACELI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_san_antonio_bajo.xlsx
+++ b/data/data_monitoreo_san_antonio_bajo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
+          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
+          <t>VASQUEZ DIAZ LUZ ANGELICA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -537,27 +537,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -578,6 +578,16 @@
       </c>
       <c r="B15" t="n">
         <v>69</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GALLARDO SAUCEDO CÉSAR MELANIO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_san_antonio_bajo.xlsx
+++ b/data/data_monitoreo_san_antonio_bajo.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SOTO VILLENA NILSON</t>
+          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GALLARDO CORTEZ MELISSA DEL CARMEN</t>
+          <t>SOTO VILLENA NILSON</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -537,23 +537,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ROJAS VASQUEZ FLOR NOELITA</t>
+          <t>TELLO FERNANDEZ MILENY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TELLO FERNANDEZ MILENY</t>
+          <t>ROJAS VASQUEZ FLOR NOELITA</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
